--- a/gte/nodes/LPC/compressor_stage_3_blade_stator_coordinates_foil.xlsx
+++ b/gte/nodes/LPC/compressor_stage_3_blade_stator_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.001607268464318143</v>
       </c>
       <c r="B2">
-        <v>0.00091496350249399637</v>
+        <v>0.00079602563613445372</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.003214536928636286</v>
       </c>
       <c r="B3">
-        <v>0.0015101197066823043</v>
+        <v>0.0013461783233218534</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.00482180539295443</v>
       </c>
       <c r="B4">
-        <v>0.0020403189896882395</v>
+        <v>0.0018416606074985172</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0064290738572725719</v>
       </c>
       <c r="B5">
-        <v>0.0025199461147550968</v>
+        <v>0.0022933212612862388</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0080363423215907143</v>
       </c>
       <c r="B6">
-        <v>0.0029549876227565612</v>
+        <v>0.0027057062604803595</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.00964361078590886</v>
       </c>
       <c r="B7">
-        <v>0.0033489335805428479</v>
+        <v>0.0030814841080803088</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.011250879250227</v>
       </c>
       <c r="B8">
-        <v>0.0037039073812846607</v>
+        <v>0.0034222958203813224</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.012858147714545144</v>
       </c>
       <c r="B9">
-        <v>0.004023102459148103</v>
+        <v>0.0037305795986422017</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.014465416178863285</v>
       </c>
       <c r="B10">
-        <v>0.0043099435606371479</v>
+        <v>0.004008944595523054</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.016072684643181429</v>
       </c>
       <c r="B11">
-        <v>0.0045677106406118518</v>
+        <v>0.0042598865843256409</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.017679953107499573</v>
       </c>
       <c r="B12">
-        <v>0.0047982099531570163</v>
+        <v>0.0044847937460631149</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.019287221571817718</v>
       </c>
       <c r="B13">
-        <v>0.0049974977409003411</v>
+        <v>0.0046807372719525212</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.020894490036135856</v>
       </c>
       <c r="B14">
-        <v>0.0051632514173796315</v>
+        <v>0.0048460019575588811</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.022501758500454</v>
       </c>
       <c r="B15">
-        <v>0.0053053830912301973</v>
+        <v>0.0049880440056352237</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.024109026964772143</v>
       </c>
       <c r="B16">
-        <v>0.0054329837167399943</v>
+        <v>0.00511370182516263</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.025716295429090288</v>
       </c>
       <c r="B17">
-        <v>0.0055396249357100242</v>
+        <v>0.0052181712428463955</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.027323563893408433</v>
       </c>
       <c r="B18">
-        <v>0.0056169769259070039</v>
+        <v>0.0052952195397528131</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.028930832357726571</v>
       </c>
       <c r="B19">
-        <v>0.0056646233214474621</v>
+        <v>0.005344542396667951</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.030538100822044716</v>
       </c>
       <c r="B20">
-        <v>0.00568412612053538</v>
+        <v>0.0053673175943078208</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.032145369286362857</v>
       </c>
       <c r="B21">
-        <v>0.0056770473213747369</v>
+        <v>0.0053647229133884358</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.033752637750681</v>
       </c>
       <c r="B22">
-        <v>0.0056446672331209131</v>
+        <v>0.0053377228147513858</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.035359906214999147</v>
       </c>
       <c r="B23">
-        <v>0.0055871394087348824</v>
+        <v>0.0052864284797405807</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.036967174679317288</v>
       </c>
       <c r="B24">
-        <v>0.0055043357121290206</v>
+        <v>0.0052107377698255063</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.038574443143635437</v>
       </c>
       <c r="B25">
-        <v>0.0053961280072156994</v>
+        <v>0.0051105485464756515</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.040181711607953571</v>
       </c>
       <c r="B26">
-        <v>0.0052623351725706747</v>
+        <v>0.0049857169166144548</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.041788980072271713</v>
       </c>
       <c r="B27">
-        <v>0.00510256414542321</v>
+        <v>0.004835931968981147</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.043396248536589861</v>
       </c>
       <c r="B28">
-        <v>0.0049163688776659538</v>
+        <v>0.0046608410377689084</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.045003517000908</v>
       </c>
       <c r="B29">
-        <v>0.0047033033211915471</v>
+        <v>0.0044600914571709255</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.046610785465226151</v>
       </c>
       <c r="B30">
-        <v>0.00446311686837511</v>
+        <v>0.0042334749911793791</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.048218053929544286</v>
       </c>
       <c r="B31">
-        <v>0.0041963406735216506</v>
+        <v>0.0039813611229824637</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.049825322393862427</v>
       </c>
       <c r="B32">
-        <v>0.0039037013314186433</v>
+        <v>0.0037042637655673727</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.051432590858180575</v>
       </c>
       <c r="B33">
-        <v>0.0035859254368535687</v>
+        <v>0.0034026968319213007</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.053039859322498717</v>
       </c>
       <c r="B34">
-        <v>0.0032434004139646317</v>
+        <v>0.003076917376618556</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.054647127786816865</v>
       </c>
       <c r="B35">
-        <v>0.0028751570042929364</v>
+        <v>0.0027261550205819008</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.056254396251135</v>
       </c>
       <c r="B36">
-        <v>0.0024798867787303161</v>
+        <v>0.0023493825263212133</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.057861664715453141</v>
       </c>
       <c r="B37">
-        <v>0.0020562813081685988</v>
+        <v>0.0019455726563463653</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.05946893317977129</v>
       </c>
       <c r="B38">
-        <v>0.0016022143760970012</v>
+        <v>0.0015130823189562514</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.061076201644089431</v>
       </c>
       <c r="B39">
-        <v>0.0011122886163942754</v>
+        <v>0.0010478050056058315</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.06268347010840758</v>
       </c>
       <c r="B40">
-        <v>0.0005802888755365573</v>
+        <v>0.0005450183535390833</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.06268347010840758</v>
       </c>
       <c r="B43">
-        <v>0.00029812469955676504</v>
+        <v>0.0003333952215542391</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.061076201644089431</v>
       </c>
       <c r="B44">
-        <v>0.00059641973008672507</v>
+        <v>0.00066090334087516892</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.05946893317977129</v>
       </c>
       <c r="B45">
-        <v>0.0008891579189710012</v>
+        <v>0.00097828997611175113</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.057861664715453141</v>
       </c>
       <c r="B46">
-        <v>0.0011706120935907297</v>
+        <v>0.0012813207454129632</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.056254396251135</v>
       </c>
       <c r="B47">
-        <v>0.0014358527594574928</v>
+        <v>0.0015663570118665956</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.054647127786816865</v>
       </c>
       <c r="B48">
-        <v>0.0016831411346046544</v>
+        <v>0.0018321431183156896</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.053039859322498717</v>
       </c>
       <c r="B49">
-        <v>0.0019115361151960278</v>
+        <v>0.002078019152542103</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.051432590858180575</v>
       </c>
       <c r="B50">
-        <v>0.0021200965973954228</v>
+        <v>0.0023033252023276908</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.049825322393862427</v>
       </c>
       <c r="B51">
-        <v>0.0023082008046084804</v>
+        <v>0.0025076383704597505</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.048218053929544286</v>
       </c>
       <c r="B52">
-        <v>0.0024765042692081627</v>
+        <v>0.0026914838197473487</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.046610785465226151</v>
       </c>
       <c r="B53">
-        <v>0.0026259818508092632</v>
+        <v>0.0028556237280049947</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.045003517000908</v>
       </c>
       <c r="B54">
-        <v>0.0027576084090265764</v>
+        <v>0.0030008202730471977</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.043396248536589861</v>
       </c>
       <c r="B55">
-        <v>0.002872146158489605</v>
+        <v>0.0031276739983866482</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.041788980072271713</v>
       </c>
       <c r="B56">
-        <v>0.0029695067338866977</v>
+        <v>0.0032361389103287624</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.040181711607953571</v>
       </c>
       <c r="B57">
-        <v>0.0030493891249209161</v>
+        <v>0.003326007380877136</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.038574443143635437</v>
       </c>
       <c r="B58">
-        <v>0.0031114923212953189</v>
+        <v>0.0033970717820353664</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.036967174679317288</v>
       </c>
       <c r="B59">
-        <v>0.0031555521737009103</v>
+        <v>0.0034491501160044242</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.035359906214999147</v>
       </c>
       <c r="B60">
-        <v>0.0031814519767804639</v>
+        <v>0.003482162905774766</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.033752637750681</v>
       </c>
       <c r="B61">
-        <v>0.0031891118861646964</v>
+        <v>0.0034960563045342233</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.032145369286362857</v>
       </c>
       <c r="B62">
-        <v>0.0031784520574843246</v>
+        <v>0.0034907764654706261</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.030538100822044716</v>
       </c>
       <c r="B63">
-        <v>0.0031496579107149073</v>
+        <v>0.0034664664369424662</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.028930832357726571</v>
       </c>
       <c r="B64">
-        <v>0.0031039759232113686</v>
+        <v>0.003424056847990881</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.027323563893408433</v>
       </c>
       <c r="B65">
-        <v>0.0030429178366734762</v>
+        <v>0.0033646752228276675</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.025716295429090288</v>
       </c>
       <c r="B66">
-        <v>0.002967995392800995</v>
+        <v>0.0032894490856646241</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.024109026964772143</v>
       </c>
       <c r="B67">
-        <v>0.0028787285841210767</v>
+        <v>0.0031980104756984414</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.022501758500454</v>
       </c>
       <c r="B68">
-        <v>0.0027666704064704052</v>
+        <v>0.0030840094920653793</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.020894490036135856</v>
       </c>
       <c r="B69">
-        <v>0.0026252557388136378</v>
+        <v>0.0029425051986343874</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.019287221571817718</v>
       </c>
       <c r="B70">
-        <v>0.0024634139893177842</v>
+        <v>0.0027801744582656037</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.017679953107499573</v>
       </c>
       <c r="B71">
-        <v>0.00229088029640581</v>
+        <v>0.0026042965034997105</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.016072684643181429</v>
       </c>
       <c r="B72">
-        <v>0.0021051181903221656</v>
+        <v>0.0024129422466083765</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.014465416178863285</v>
       </c>
       <c r="B73">
-        <v>0.0019019518397243895</v>
+        <v>0.0022029508048384844</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.012858147714545144</v>
       </c>
       <c r="B74">
-        <v>0.0016829195751008877</v>
+        <v>0.00197544243560679</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.011250879250227</v>
       </c>
       <c r="B75">
-        <v>0.001451014894057951</v>
+        <v>0.0017326264549612897</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.00964361078590886</v>
       </c>
       <c r="B76">
-        <v>0.001209337800842536</v>
+        <v>0.001476787273305075</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0080363423215907143</v>
       </c>
       <c r="B77">
-        <v>0.000960736724546949</v>
+        <v>0.0012100180868231507</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0064290738572725719</v>
       </c>
       <c r="B78">
-        <v>0.00070694728700423177</v>
+        <v>0.00093357214047309</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.00482180539295443</v>
       </c>
       <c r="B79">
-        <v>0.00045105193217045991</v>
+        <v>0.00064971031436018237</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.003214536928636286</v>
       </c>
       <c r="B80">
-        <v>0.00019858863979869976</v>
+        <v>0.00036253002315915039</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.001607268464318143</v>
       </c>
       <c r="B81">
-        <v>-3.6539428382344216E-05</v>
+        <v>8.239843797719842E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.001781123102526175</v>
       </c>
       <c r="B2">
-        <v>0.001312281072493972</v>
+        <v>0.0011804779629070352</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.00356224620505235</v>
       </c>
       <c r="B3">
-        <v>0.0021041250335625018</v>
+        <v>0.0019224504771048322</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0053433693075785249</v>
       </c>
       <c r="B4">
-        <v>0.0027990824445179733</v>
+        <v>0.0025789356290457379</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0071244924101047</v>
       </c>
       <c r="B5">
-        <v>0.0034209939368014665</v>
+        <v>0.0031698555793452762</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0089056155126308739</v>
       </c>
       <c r="B6">
-        <v>0.0039797443185306007</v>
+        <v>0.003703498748337261</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.01068673861515705</v>
       </c>
       <c r="B7">
-        <v>0.0044810739388797876</v>
+        <v>0.0041846950546194318</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.012467861717683224</v>
       </c>
       <c r="B8">
-        <v>0.0049284540399360888</v>
+        <v>0.0046163811857746762</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0142489848202094</v>
       </c>
       <c r="B9">
-        <v>0.0053271403574787716</v>
+        <v>0.0050029759528190084</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.016030107922735574</v>
       </c>
       <c r="B10">
-        <v>0.0056827759476920934</v>
+        <v>0.0053492185971292412</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.017811231025261748</v>
       </c>
       <c r="B11">
-        <v>0.0060007686546880911</v>
+        <v>0.0056596479580922785</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.019592354127787925</v>
       </c>
       <c r="B12">
-        <v>0.0062840793505603608</v>
+        <v>0.0059367616127001229</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0213734772303141</v>
       </c>
       <c r="B13">
-        <v>0.00652611623140095</v>
+        <v>0.0061750924903550908</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.023154600332840274</v>
       </c>
       <c r="B14">
-        <v>0.0067229850186189544</v>
+        <v>0.006371419393650133</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.024935723435366448</v>
       </c>
       <c r="B15">
-        <v>0.0068911342108931919</v>
+        <v>0.006539469265530424</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.026716846537892622</v>
       </c>
       <c r="B16">
-        <v>0.0070456497066247233</v>
+        <v>0.0066918318062978129</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.0284979696404188</v>
       </c>
       <c r="B17">
-        <v>0.0071758242258338489</v>
+        <v>0.0068195996053286136</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.030279092742944973</v>
       </c>
       <c r="B18">
-        <v>0.0072677928560683086</v>
+        <v>0.0069112316924479</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.032060215845471148</v>
       </c>
       <c r="B19">
-        <v>0.0073208533333663514</v>
+        <v>0.0069661499702013251</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.033841338947997325</v>
       </c>
       <c r="B20">
-        <v>0.0073375940558888511</v>
+        <v>0.0069865170593146923</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.035622462050523496</v>
       </c>
       <c r="B21">
-        <v>0.0073206034217966837</v>
+        <v>0.0069744955805137983</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.037403585153049673</v>
       </c>
       <c r="B22">
-        <v>0.0072720042188982982</v>
+        <v>0.0069318583086869926</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.039184708255575851</v>
       </c>
       <c r="B23">
-        <v>0.007192056793592437</v>
+        <v>0.0068588186353728152</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.040965831358102021</v>
       </c>
       <c r="B24">
-        <v>0.0070805558819254134</v>
+        <v>0.0067552001062723523</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.0427469544606282</v>
       </c>
       <c r="B25">
-        <v>0.0069372962199435425</v>
+        <v>0.0066208262670866928</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.04452807756315437</v>
       </c>
       <c r="B26">
-        <v>0.0067619870168584154</v>
+        <v>0.00645544758228229</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.046309200665680547</v>
       </c>
       <c r="B27">
-        <v>0.0065539953745427067</v>
+        <v>0.0062585221913870441</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.048090323768206725</v>
       </c>
       <c r="B28">
-        <v>0.0063126028680343714</v>
+        <v>0.0060294351526942258</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.049871446870732895</v>
       </c>
       <c r="B29">
-        <v>0.0060370910723713611</v>
+        <v>0.0057675715244971011</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.051652569973259073</v>
       </c>
       <c r="B30">
-        <v>0.0057270690568528215</v>
+        <v>0.0054725873309550178</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.053433693075785244</v>
       </c>
       <c r="B31">
-        <v>0.005383455867822684</v>
+        <v>0.005145222459691655</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.055214816178311421</v>
       </c>
       <c r="B32">
-        <v>0.0050074980458860658</v>
+        <v>0.0047864877641967648</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.0569959392808376</v>
       </c>
       <c r="B33">
-        <v>0.0046004421316480923</v>
+        <v>0.0043973940979601086</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.058777062383363769</v>
       </c>
       <c r="B34">
-        <v>0.0041629736967153108</v>
+        <v>0.0039784825612399315</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.060558185485889947</v>
       </c>
       <c r="B35">
-        <v>0.0036935344366999731</v>
+        <v>0.0035284152413684444</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.062339308588416117</v>
       </c>
       <c r="B36">
-        <v>0.0031900050782157586</v>
+        <v>0.0030453844724463476</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.0641204316909423</v>
       </c>
       <c r="B37">
-        <v>0.0026502663478763402</v>
+        <v>0.0025275825885743373</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.065901554793468473</v>
       </c>
       <c r="B38">
-        <v>0.0020708422185416442</v>
+        <v>0.0019720689459530962</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.06768267789599465</v>
       </c>
       <c r="B39">
-        <v>0.0014428296480565809</v>
+        <v>0.001371370989183231</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.069463800998520828</v>
       </c>
       <c r="B40">
-        <v>0.00075596884051230741</v>
+        <v>0.00071688318496532981</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.071244924101046991</v>
       </c>
       <c r="B41">
-        <v>-1.5572370540166275E-17</v>
+        <v>-1.5819551024930821E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.069463800998520828</v>
       </c>
       <c r="B43">
-        <v>0.00028694097394857621</v>
+        <v>0.00032602662949555376</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.06768267789599465</v>
       </c>
       <c r="B44">
-        <v>0.00058532574157638107</v>
+        <v>0.000656784400449731</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.065901554793468473</v>
       </c>
       <c r="B45">
-        <v>0.00088556294747906754</v>
+        <v>0.00098433622006761554</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.0641204316909423</v>
       </c>
       <c r="B46">
-        <v>0.0011780612362523053</v>
+        <v>0.0013007449955543082</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.062339308588416117</v>
       </c>
       <c r="B47">
-        <v>0.0014545578089828284</v>
+        <v>0.0015991784147522394</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.060558185485889947</v>
       </c>
       <c r="B48">
-        <v>0.001712104092721628</v>
+        <v>0.0018772232880531572</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.058777062383363769</v>
       </c>
       <c r="B49">
-        <v>0.0019490800710107621</v>
+        <v>0.0021335712064861415</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.0569959392808376</v>
       </c>
       <c r="B50">
-        <v>0.0021638657273922854</v>
+        <v>0.0023669137610802691</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.055214816178311421</v>
       </c>
       <c r="B51">
-        <v>0.0023553746656144541</v>
+        <v>0.0025763849473037551</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.053433693075785244</v>
       </c>
       <c r="B52">
-        <v>0.0025246549702503287</v>
+        <v>0.0027628883783813582</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.051652569973259073</v>
       </c>
       <c r="B53">
-        <v>0.0026732883460791677</v>
+        <v>0.0029277700719769718</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.049871446870732895</v>
       </c>
       <c r="B54">
-        <v>0.002802856497880233</v>
+        <v>0.0030723760457544934</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.048090323768206725</v>
       </c>
       <c r="B55">
-        <v>0.0029145902839526178</v>
+        <v>0.0031977579992927638</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.046309200665680547</v>
       </c>
       <c r="B56">
-        <v>0.0030083171766747533</v>
+        <v>0.0033037903598304155</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.04452807756315437</v>
       </c>
       <c r="B57">
-        <v>0.0030835138019449045</v>
+        <v>0.00339005323652103</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.0427469544606282</v>
       </c>
       <c r="B58">
-        <v>0.0031396567856613357</v>
+        <v>0.0034561267385181853</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.040965831358102021</v>
       </c>
       <c r="B59">
-        <v>0.00317628657408867</v>
+        <v>0.0035016423497417314</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.039184708255575851</v>
       </c>
       <c r="B60">
-        <v>0.0031931988949569596</v>
+        <v>0.0035264370531765828</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.037403585153049673</v>
       </c>
       <c r="B61">
-        <v>0.0031902532963626164</v>
+        <v>0.0035303992065739229</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.035622462050523496</v>
       </c>
       <c r="B62">
-        <v>0.0031673093264020496</v>
+        <v>0.0035134171676849354</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.033841338947997325</v>
       </c>
       <c r="B63">
-        <v>0.0031246700969989397</v>
+        <v>0.0034757470935730984</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.032060215845471148</v>
       </c>
       <c r="B64">
-        <v>0.0030644129753860465</v>
+        <v>0.0034191163385510715</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.030279092742944973</v>
       </c>
       <c r="B65">
-        <v>0.0029890588926234003</v>
+        <v>0.0033456200562438092</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.0284979696404188</v>
       </c>
       <c r="B66">
-        <v>0.00290112877977103</v>
+        <v>0.0032573534002762645</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.026716846537892622</v>
       </c>
       <c r="B67">
-        <v>0.0027998349027018076</v>
+        <v>0.0031536528030287172</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.024935723435366448</v>
       </c>
       <c r="B68">
-        <v>0.0026711548665399767</v>
+        <v>0.0030228198119027442</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.023154600332840274</v>
       </c>
       <c r="B69">
-        <v>0.0025041975189930973</v>
+        <v>0.0028557631439619182</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0213734772303141</v>
       </c>
       <c r="B70">
-        <v>0.0023138313388506473</v>
+        <v>0.0026648550798965055</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.019592354127787925</v>
       </c>
       <c r="B71">
-        <v>0.0021162664962375158</v>
+        <v>0.002463584234097752</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.017811231025261748</v>
       </c>
       <c r="B72">
-        <v>0.0019073202955383352</v>
+        <v>0.0022484409921341478</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.016030107922735574</v>
       </c>
       <c r="B73">
-        <v>0.0016800877409378623</v>
+        <v>0.0020136450915007147</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0142489848202094</v>
       </c>
       <c r="B74">
-        <v>0.0014371675015616059</v>
+        <v>0.0017613319062213695</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.012467861717683224</v>
       </c>
       <c r="B75">
-        <v>0.0011835797899991366</v>
+        <v>0.0014956526441605494</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.01068673861515705</v>
       </c>
       <c r="B76">
-        <v>0.00092452732775552115</v>
+        <v>0.0012209062120158768</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0089056155126308739</v>
       </c>
       <c r="B77">
-        <v>0.00066479747621052063</v>
+        <v>0.00094104304640386059</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0071244924101047</v>
       </c>
       <c r="B78">
-        <v>0.00040733364732717934</v>
+        <v>0.00065847200478336978</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0053433693075785249</v>
       </c>
       <c r="B79">
-        <v>0.00015732065885115047</v>
+        <v>0.00037746747432338551</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.00356224620505235</v>
       </c>
       <c r="B80">
-        <v>-7.59696439295355E-05</v>
+        <v>0.00010570491252813422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.001781123102526175</v>
       </c>
       <c r="B81">
-        <v>-0.000269356242549271</v>
+        <v>-0.00013755313296233407</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0019287221571817716</v>
       </c>
       <c r="B2">
-        <v>0.0017208886772379678</v>
+        <v>0.001578163237606517</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0038574443143635432</v>
       </c>
       <c r="B3">
-        <v>0.00269985273927384</v>
+        <v>0.0025031230792412992</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0057861664715453155</v>
       </c>
       <c r="B4">
-        <v>0.003548328050601937</v>
+        <v>0.0033099379919742703</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0077148886287270865</v>
       </c>
       <c r="B5">
-        <v>0.0043006460649928184</v>
+        <v>0.0040286962408301891</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0096436107859088575</v>
       </c>
       <c r="B6">
-        <v>0.0049709945292223312</v>
+        <v>0.00467185689449089</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.011572332943090631</v>
       </c>
       <c r="B7">
-        <v>0.0055675848585544979</v>
+        <v>0.0052466454915994516</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.013501055100272401</v>
       </c>
       <c r="B8">
-        <v>0.0060953559467135142</v>
+        <v>0.0057574220736295095</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.015429777257454173</v>
       </c>
       <c r="B9">
-        <v>0.0065618311146021305</v>
+        <v>0.006210803681995049</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.017358499414635943</v>
       </c>
       <c r="B10">
-        <v>0.006975096676292516</v>
+        <v>0.0066138979181556007</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.019287221571817715</v>
       </c>
       <c r="B11">
-        <v>0.0073429064913559765</v>
+        <v>0.0069735176238125227</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.021215943728999487</v>
       </c>
       <c r="B12">
-        <v>0.0076694848902131444</v>
+        <v>0.0072933854417004621</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.023144665886181262</v>
       </c>
       <c r="B13">
-        <v>0.0079452705411828</v>
+        <v>0.0075651579784454161</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.02507338804336303</v>
       </c>
       <c r="B14">
-        <v>0.0081646002885872246</v>
+        <v>0.0077839009368023265</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.027002110200544802</v>
       </c>
       <c r="B15">
-        <v>0.0083511893428645477</v>
+        <v>0.007970382440150579</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.028930832357726574</v>
       </c>
       <c r="B16">
-        <v>0.0085267884693082</v>
+        <v>0.0081436501994153632</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.030859554514908346</v>
       </c>
       <c r="B17">
-        <v>0.008675912286517</v>
+        <v>0.0082901678550806462</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.032788276672090118</v>
       </c>
       <c r="B18">
-        <v>0.0087785200544032473</v>
+        <v>0.0083924111910182175</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.034716998829271886</v>
       </c>
       <c r="B19">
-        <v>0.0088335857448277877</v>
+        <v>0.0084494886350923743</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.036645720986453661</v>
       </c>
       <c r="B20">
-        <v>0.00884483700763861</v>
+        <v>0.00846466677616554</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.03857444314363543</v>
       </c>
       <c r="B21">
-        <v>0.0088160014926837015</v>
+        <v>0.0084412122031001409</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.040503165300817205</v>
       </c>
       <c r="B22">
-        <v>0.0087501377092792376</v>
+        <v>0.0083818044072358055</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.042431887457998974</v>
       </c>
       <c r="B23">
-        <v>0.0086476276046141536</v>
+        <v>0.0082867744898209913</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.044360609615180749</v>
       </c>
       <c r="B24">
-        <v>0.0085081839853455733</v>
+        <v>0.0081558664545813564</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.046289331772362524</v>
       </c>
       <c r="B25">
-        <v>0.008331519658130622</v>
+        <v>0.0079888243052425641</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.048218053929544286</v>
       </c>
       <c r="B26">
-        <v>0.0081172270004222415</v>
+        <v>0.0077852850932747762</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.050146776086726061</v>
       </c>
       <c r="B27">
-        <v>0.0078644166728566185</v>
+        <v>0.0075444580611261428</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.052075498243907836</v>
       </c>
       <c r="B28">
-        <v>0.0075720789068657677</v>
+        <v>0.0072654454989893166</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.054004220401089605</v>
       </c>
       <c r="B29">
-        <v>0.0072392039338816955</v>
+        <v>0.00694734969705695</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.05593294255827138</v>
       </c>
       <c r="B30">
-        <v>0.0068652580737808121</v>
+        <v>0.0065896878211459346</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.057861664715453148</v>
       </c>
       <c r="B31">
-        <v>0.0064516120002171534</v>
+        <v>0.0061936365395701305</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.059790386872634917</v>
       </c>
       <c r="B32">
-        <v>0.0060001124752891528</v>
+        <v>0.0057607873962676279</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.061719109029816692</v>
       </c>
       <c r="B33">
-        <v>0.0055126062610952467</v>
+        <v>0.0052927319351765249</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.06364783118699846</v>
       </c>
       <c r="B34">
-        <v>0.0049901338818519351</v>
+        <v>0.0047903542370366448</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.065576553344180236</v>
       </c>
       <c r="B35">
-        <v>0.004430510910247959</v>
+        <v>0.0042517085297947167</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.067505275501362</v>
       </c>
       <c r="B36">
-        <v>0.0038307466810901221</v>
+        <v>0.0036741415781991991</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.069433997658543772</v>
       </c>
       <c r="B37">
-        <v>0.0031878505291852237</v>
+        <v>0.0030550001469985435</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.071362719815725548</v>
       </c>
       <c r="B38">
-        <v>0.0024968765801177076</v>
+        <v>0.0023899181115488079</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.073291441972907323</v>
       </c>
       <c r="B39">
-        <v>0.0017450581225825724</v>
+        <v>0.0016676777896364396</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.0752201641300891</v>
       </c>
       <c r="B40">
-        <v>0.00091767323605245583</v>
+        <v>0.00087534860965548665</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.07714888628727086</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>-2.6766396837598787E-19</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.07714888628727086</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-6.6915992093996967E-20</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.0752201641300891</v>
       </c>
       <c r="B43">
-        <v>0.00024047921370095465</v>
+        <v>0.00028280384009792345</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.073291441972907323</v>
       </c>
       <c r="B44">
-        <v>0.00050697279544445191</v>
+        <v>0.00058435312839058443</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.071362719815725548</v>
       </c>
       <c r="B45">
-        <v>0.00078554108301530715</v>
+        <v>0.00089249955158420707</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.069433997658543772</v>
       </c>
       <c r="B46">
-        <v>0.0010622444141983373</v>
+        <v>0.0011950947963850177</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.067505275501362</v>
       </c>
       <c r="B47">
-        <v>0.0013250650348353454</v>
+        <v>0.001481670137726269</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.065576553344180236</v>
       </c>
       <c r="B48">
-        <v>0.0015696728229960817</v>
+        <v>0.001748475203449324</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.06364783118699846</v>
       </c>
       <c r="B49">
-        <v>0.0017936595648072862</v>
+        <v>0.0019934392096225772</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.061719109029816692</v>
       </c>
       <c r="B50">
-        <v>0.0019946170463956956</v>
+        <v>0.0022144913723144174</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.059790386872634917</v>
       </c>
       <c r="B51">
-        <v>0.0021709112109447606</v>
+        <v>0.002410236289966285</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.057861664715453148</v>
       </c>
       <c r="B52">
-        <v>0.0023240046298647838</v>
+        <v>0.002581980090511807</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.05593294255827138</v>
       </c>
       <c r="B53">
-        <v>0.00245613403162278</v>
+        <v>0.0027317042842576566</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.054004220401089605</v>
       </c>
       <c r="B54">
-        <v>0.002569536144685765</v>
+        <v>0.0028613903815105104</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.052075498243907836</v>
       </c>
       <c r="B55">
-        <v>0.0026659443808425328</v>
+        <v>0.0029725777887189843</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.050146776086726061</v>
       </c>
       <c r="B56">
-        <v>0.0027450788851689895</v>
+        <v>0.0030650374968994656</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.048218053929544286</v>
       </c>
       <c r="B57">
-        <v>0.00280615648606282</v>
+        <v>0.0031380983932102835</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.046289331772362524</v>
       </c>
       <c r="B58">
-        <v>0.002848394011921709</v>
+        <v>0.0031910893648097664</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.044360609615180749</v>
       </c>
       <c r="B59">
-        <v>0.0028711034931181104</v>
+        <v>0.0032234210238823269</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.042431887457998974</v>
       </c>
       <c r="B60">
-        <v>0.0028739777679235492</v>
+        <v>0.003234830882716712</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.040503165300817205</v>
       </c>
       <c r="B61">
-        <v>0.0028568048765843191</v>
+        <v>0.0032251381786277513</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.03857444314363543</v>
       </c>
       <c r="B62">
-        <v>0.0028193728593467128</v>
+        <v>0.0031941621489302743</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.036645720986453661</v>
       </c>
       <c r="B63">
-        <v>0.0027621133040694767</v>
+        <v>0.0031422835355425474</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.034716998829271886</v>
       </c>
       <c r="B64">
-        <v>0.0026880319890611637</v>
+        <v>0.0030721290987965775</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.032788276672090118</v>
       </c>
       <c r="B65">
-        <v>0.0026007782402427803</v>
+        <v>0.0029868871036278092</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.030859554514908346</v>
       </c>
       <c r="B66">
-        <v>0.0025040013835353316</v>
+        <v>0.0028897458149716856</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.028930832357726574</v>
       </c>
       <c r="B67">
-        <v>0.0023965761510227968</v>
+        <v>0.0027797144209156343</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.027002110200544802</v>
       </c>
       <c r="B68">
-        <v>0.0022582788994410445</v>
+        <v>0.0026390858021550132</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.02507338804336303</v>
       </c>
       <c r="B69">
-        <v>0.0020734106600288423</v>
+        <v>0.0024541100118137412</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.023144665886181262</v>
       </c>
       <c r="B70">
-        <v>0.0018634695373846632</v>
+        <v>0.002243582100122047</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.021215943728999487</v>
       </c>
       <c r="B71">
-        <v>0.0016518937140102506</v>
+        <v>0.0020279931625229314</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.019287221571817715</v>
       </c>
       <c r="B72">
-        <v>0.0014326846106607301</v>
+        <v>0.001802073478204183</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.017358499414635943</v>
       </c>
       <c r="B73">
-        <v>0.0011959165461018937</v>
+        <v>0.0015571153042388075</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.015429777257454173</v>
       </c>
       <c r="B74">
-        <v>0.000945392192888812</v>
+        <v>0.0012964196254958943</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.013501055100272401</v>
       </c>
       <c r="B75">
-        <v>0.00068841397736941025</v>
+        <v>0.0010263478504534166</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.011572332943090631</v>
       </c>
       <c r="B76">
-        <v>0.000432554987273749</v>
+        <v>0.00075349435422879555</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0096436107859088575</v>
       </c>
       <c r="B77">
-        <v>0.00018479237351926177</v>
+        <v>0.00048393000825070365</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0077148886287270865</v>
       </c>
       <c r="B78">
-        <v>-5.0551121609257337E-05</v>
+        <v>0.00022139870255337248</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0057861664715453155</v>
       </c>
       <c r="B79">
-        <v>-0.00026591288744073449</v>
+        <v>-2.7522828813067868E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0038574443143635432</v>
       </c>
       <c r="B80">
-        <v>-0.00044782182124681095</v>
+        <v>-0.00025109216121427025</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0019287221571817716</v>
       </c>
       <c r="B81">
-        <v>-0.00056271835686524973</v>
+        <v>-0.00041999291723379868</v>
       </c>
     </row>
     <row r="82" spans="1:2">
